--- a/02_DIA_inicio_2026_analisis_assets/rbd_9699_colegio-naciones-unidas_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9699_colegio-naciones-unidas_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F56036FD-38B8-424C-9231-5E79BA22067D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4537C496-193E-4AD5-AD43-819B78A651B3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2339E151-7E44-442B-9612-128CCD87FF4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{937DFC32-A9CD-411C-A2C2-14CBDB15746B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{946D206D-3320-4D12-8D1B-A71CB2D84133}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80A8D8D7-BD58-42BB-BC05-47B6EF205A23}"/>
 </file>